--- a/stories/arbres/ATOM-SAN.SOM.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir arrive. La maison est calme. Maman dit : Simon, c'est l'heure. Simon va dans sa chambre. Il prend son pyjama. Le pyjama est doux. Simon met le pyjama. Les manches sont chaudes. Papa ouvre le lit. Simon se couche. Il pose la tête. Papa raconte une petite histoire. Simon écoute. Maman dit : c'est le dodo. Le corps a besoin de dormir. Simon ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Simon est au lit.</t>
+          <t>Le soir arrive. La maison est calme. Simon, c'est l'heure. Simon va dans sa chambre. Il prend son pyjama. Le pyjama est doux. Simon met le pyjama. Les manches sont chaudes. Papa ouvre le lit. Simon se couche. Il pose la tête. Papa raconte une petite histoire. Simon écoute. C'est le dodo. Le corps a besoin de dormir. Simon ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Simon est au lit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir arrive. La maison est calme.
+maman|Simon, c'est l'heure.
+narrateur|Simon va dans sa chambre. Il prend son pyjama. Le pyjama est doux. Simon met le pyjama. Les manches sont chaudes. Papa ouvre le lit. Simon se couche. Il pose la tête. Papa raconte une petite histoire. Simon écoute.
+maman|C'est le dodo.
+narrateur|Le corps a besoin de dormir. Simon ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Simon est au lit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Simon va dormir. Que met-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Simon a mis le pyjama. Il s'est couché. Le soir, c'est le dodo. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Simon dort. Le pyjama est chaud. La chambre est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Le corps a besoin de dormir. Simon ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Simon est au lit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Simon va dormir. Que met-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Simon a mis le pyjama. Il s'est couché. Le soir, c'est le dodo. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Simon dort. Le pyjama est chaud. La chambre est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.SOM.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Simon met le pyjama</t>
+          <t>L'étoile jaune d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une étoile jaune veille près du lit. Amir met le pyjama gris. Papa raconte l'étoile. Amir se couche. Soir, pyjama, dodo.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir arrive. La maison est calme. Simon, c'est l'heure. Simon va dans sa chambre. Il prend son pyjama. Le pyjama est doux. Simon met le pyjama. Les manches sont chaudes. Papa ouvre le lit. Simon se couche. Il pose la tête. Papa raconte une petite histoire. Simon écoute. C'est le dodo. Le corps a besoin de dormir. Simon ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Simon est au lit.</t>
+          <t>Une petite étoile jaune veille. Elle est collée près du lit. Elle fait un rond sur le mur. Les pantoufles attendent par terre. L'une touche l'autre. Dehors, un oiseau se tait. La rue devient calme. Ça sent le linge propre. Amir vit ici, avec papa et maman. En ce moment, le pyjama attend. Amir, c'est l'heure. L'heure de quoi, maman ? L'heure du pyjama. Puis l'heure du dodo. Amir va vers la chaise. Le pyjama est gris, tout doux. Il est chaud, maman. Oui. Mets le pyjama. Amir glisse un bras. Puis l'autre bras. Les manches sont chaudes. Bravo, Amir. Tu as mis le pyjama. Viens. J'ouvre le lit. Papa ouvre la couverture. L'oreiller sent le propre. Amir se couche. Il pose la tête. L'étoile veille, papa. Oui. Elle veille. Tu veux une petite histoire ? Oui. Une courte. Papa raconte une étoile. L'étoile marche tout doucement. Amir écoute. C'est le dodo. Le corps a besoin de dormir. C'est le soir. Le soir, on se couche. Pyjama, puis dodo. Oui. Bravo. Tu as fait du bon travail. Amir ferme les yeux. Il respire doucement. L'étoile jaune reste allumée. Amir est au lit. C'est le soir. C'est le dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soir arrive. La maison est calme.
-maman|Simon, c'est l'heure.
-narrateur|Simon va dans sa chambre. Il prend son pyjama. Le pyjama est doux. Simon met le pyjama. Les manches sont chaudes. Papa ouvre le lit. Simon se couche. Il pose la tête. Papa raconte une petite histoire. Simon écoute.
+          <t>narrateur|Une petite étoile jaune veille.
+narrateur|Elle est collée près du lit.
+narrateur|Elle fait un rond sur le mur.
+narrateur|Les pantoufles attendent par terre.
+narrateur|L'une touche l'autre.
+narrateur|Dehors, un oiseau se tait.
+narrateur|La rue devient calme.
+narrateur|Ça sent le linge propre.
+narrateur|Amir vit ici, avec papa et maman.
+narrateur|En ce moment, le pyjama attend.
+maman|Amir, c'est l'heure.
+enfant-m|L'heure de quoi, maman ?
+maman|L'heure du pyjama.
+maman|Puis l'heure du dodo.
+narrateur|Amir va vers la chaise.
+narrateur|Le pyjama est gris, tout doux.
+enfant-m|Il est chaud, maman.
+maman|Oui. Mets le pyjama.
+narrateur|Amir glisse un bras.
+narrateur|Puis l'autre bras.
+narrateur|Les manches sont chaudes.
+maman|Bravo, Amir.
+maman|Tu as mis le pyjama.
+papa|Viens. J'ouvre le lit.
+narrateur|Papa ouvre la couverture.
+narrateur|L'oreiller sent le propre.
+narrateur|Amir se couche.
+narrateur|Il pose la tête.
+enfant-m|L'étoile veille, papa.
+papa|Oui. Elle veille.
+papa|Tu veux une petite histoire ?
+enfant-m|Oui. Une courte.
+narrateur|Papa raconte une étoile.
+narrateur|L'étoile marche tout doucement.
+narrateur|Amir écoute.
 maman|C'est le dodo.
-narrateur|Le corps a besoin de dormir. Simon ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Simon est au lit.</t>
+maman|Le corps a besoin de dormir.
+papa|C'est le soir.
+papa|Le soir, on se couche.
+enfant-m|Pyjama, puis dodo.
+papa|Oui. Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Amir ferme les yeux.
+narrateur|Il respire doucement.
+narrateur|L'étoile jaune reste allumée.
+narrateur|Amir est au lit.
+narrateur|C'est le soir.
+narrateur|C'est le dodo.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1399,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Simon va dormir. Que met-il ?</t>
+          <t>Amir va dormir. Que met-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1555,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Simon va dormir. Que met-il ?</t>
+          <t>narrateur|Amir va dormir.
+narrateur|Que met-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Simon a mis le pyjama. Il s'est couché. Le soir, c'est le dodo. Papa et maman sont là.</t>
+          <t>Amir a mis le pyjama. Il s'est couché. Tu as mis le pyjama ? Oui. Le gris. Bravo, Amir. Le soir, c'est le dodo. L'étoile fait encore son rond.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1728,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Simon a mis le pyjama. Il s'est couché. Le soir, c'est le dodo. Papa et maman sont là.</t>
+          <t>narrateur|Amir a mis le pyjama.
+narrateur|Il s'est couché.
+maman|Tu as mis le pyjama ?
+enfant-m|Oui. Le gris.
+maman|Bravo, Amir.
+papa|Le soir, c'est le dodo.
+narrateur|L'étoile fait encore son rond.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1762,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Simon dort. Le pyjama est chaud. La chambre est calme.</t>
+          <t>Tu es bien couché ? Oui, papa. Papa reste un moment. Maman baisse un peu l'étoile. Le rond devient tout petit. Amir respire. Le pyjama est chaud. Les pantoufles attendent encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1902,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Simon dort. Le pyjama est chaud. La chambre est calme.</t>
+          <t>papa|Tu es bien couché ?
+enfant-m|Oui, papa.
+narrateur|Papa reste un moment.
+narrateur|Maman baisse un peu l'étoile.
+narrateur|Le rond devient tout petit.
+narrateur|Amir respire.
+narrateur|Le pyjama est chaud.
+narrateur|Les pantoufles attendent encore.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1937,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Bravo. Tu as fait du bon travail. L'étoile veille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2077,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai mis le pyjama.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|L'étoile veille.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2141,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une petite étoile jaune veille. Elle est collée près du lit. Elle fait un rond sur le mur. Les pantoufles attendent par terre. L'une touche l'autre. Dehors, un oiseau se tait. La rue devient calme. Ça sent le linge propre. Amir vit ici, avec papa et maman. En ce moment, le pyjama attend. Amir, c'est l'heure. L'heure de quoi, maman ? L'heure du pyjama. Puis l'heure du dodo. Amir va vers la chaise. Le pyjama est gris, tout doux. Il est chaud, maman. Oui. Mets le pyjama. Amir glisse un bras. Puis l'autre bras. Les manches sont chaudes. Bravo, Amir. Tu as mis le pyjama. Viens. J'ouvre le lit. Papa ouvre la couverture. L'oreiller sent le propre. Amir se couche. Il pose la tête. L'étoile veille, papa. Oui. Elle veille. Tu veux une petite histoire ? Oui. Une courte. Papa raconte une étoile. L'étoile marche tout doucement. Amir écoute. C'est le dodo. Le corps a besoin de dormir. C'est le soir. Le soir, on se couche. Pyjama, puis dodo. Oui. Bravo. Tu as fait du bon travail. Amir ferme les yeux. Il respire doucement. L'étoile jaune reste allumée. Amir est au lit. C'est le soir. C'est le dodo.</t>
+          <t>Une petite étoile jaune veille. Elle est collée près du lit. Elle fait un rond sur le mur. Le rond est tiède, tout pâle. Les pantoufles attendent par terre. L'une touche l'autre. Une semelle est un peu usée. Dehors, un oiseau se tait. La rue devient calme. Un volet claque, tout loin. Ça sent le linge propre. Le rideau a un ourlet bleu. Amir vit ici, avec papa et maman. En ce moment, le pyjama attend. Amir, c'est l'heure. L'heure de quoi, maman ? L'heure du pyjama. Puis l'heure du dodo. Amir va vers la chaise. Le pyjama est gris, tout doux. Il est chaud, maman. Oui. Mets le pyjama. Amir glisse un bras. Puis l'autre bras. Les manches sont chaudes. Le col touche le cou, tout doux. Ça chatouille un peu. C'est le col. C'est doux. Bravo, Amir. Tu as mis le pyjama. Viens. J'ouvre le lit. Papa ouvre la couverture. L'oreiller sent le propre. Amir se couche. Il pose la tête. L'étoile veille, papa. Oui. Elle veille. Tu veux une petite histoire ? Oui. Une courte. Papa raconte une étoile. L'étoile marche tout doucement. Elle pose un pied, puis l'autre. Elle va où, papa ? Vers le mur. Tout près. Amir écoute. C'est le dodo. Le corps a besoin de dormir. C'est le soir. Le soir, on se couche. Pyjama, puis dodo. Oui. Bravo. Amir ferme les yeux. Il respire doucement. L'étoile jaune reste allumée. Amir est au lit. C'est le soir. C'est le dodo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt; arrive. La maison est calme. Maman dit : Simon, c'est l'heure. Simon va dans sa chambre. Il prend son pyjama. Le pyjama est doux. Simon met le pyjama. Les manches sont chaudes. Papa ouvre le lit. Simon se couche. Il pose la tête. Papa raconte une petite histoire. Simon écoute. Maman dit : c'est le dodo. Le corps a besoin de dormir. Simon ferme les yeux. Il respire doucement. C'est le soir. C'est le dodo. Simon est au lit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une petite étoile jaune veille. Elle est collée près du lit. Elle fait un rond sur le mur. Le rond est tiède, tout pâle. Les pantoufles attendent par terre. L'une touche l'autre. Une semelle est un peu usée. Dehors, un oiseau se tait. La rue devient calme. Un volet claque, tout loin. Ça sent le linge propre. Le rideau a un ourlet bleu. Amir vit ici, avec papa et maman. En ce moment, le pyjama attend. Amir, c'est l'heure. L'heure de quoi, maman ? L'heure du pyjama. Puis l'heure du dodo. Amir va vers la chaise. Le pyjama est gris, tout doux. Il est chaud, maman. Oui. Mets le pyjama. Amir glisse un bras. Puis l'autre bras. Les manches sont chaudes. Le col touche le cou, tout doux. Ça chatouille un peu. C'est le col. C'est doux. Bravo, Amir. Tu as mis le pyjama. Viens. J'ouvre le lit. Papa ouvre la couverture. L'oreiller sent le propre. Amir se couche. Il pose la tête. L'étoile veille, papa. Oui. Elle veille. Tu veux une petite histoire ? Oui. Une courte. Papa raconte une étoile. L'étoile marche tout doucement. Elle pose un pied, puis l'autre. Elle va où, papa ? Vers le mur. Tout près. Amir écoute. C'est le dodo. Le corps a besoin de dormir. C'est le soir. Le soir, on se couche. Pyjama, puis dodo. Oui. Bravo. Amir ferme les yeux. Il respire doucement. L'étoile jaune reste allumée. Amir est au lit. C'est le soir. C'est le dodo.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1327,11 +1327,15 @@
           <t>narrateur|Une petite étoile jaune veille.
 narrateur|Elle est collée près du lit.
 narrateur|Elle fait un rond sur le mur.
+narrateur|Le rond est tiède, tout pâle.
 narrateur|Les pantoufles attendent par terre.
 narrateur|L'une touche l'autre.
+narrateur|Une semelle est un peu usée.
 narrateur|Dehors, un oiseau se tait.
 narrateur|La rue devient calme.
+narrateur|Un volet claque, tout loin.
 narrateur|Ça sent le linge propre.
+narrateur|Le rideau a un ourlet bleu.
 narrateur|Amir vit ici, avec papa et maman.
 narrateur|En ce moment, le pyjama attend.
 maman|Amir, c'est l'heure.
@@ -1345,6 +1349,10 @@
 narrateur|Amir glisse un bras.
 narrateur|Puis l'autre bras.
 narrateur|Les manches sont chaudes.
+narrateur|Le col touche le cou, tout doux.
+enfant-m|Ça chatouille un peu.
+maman|C'est le col.
+maman|C'est doux.
 maman|Bravo, Amir.
 maman|Tu as mis le pyjama.
 papa|Viens. J'ouvre le lit.
@@ -1358,6 +1366,9 @@
 enfant-m|Oui. Une courte.
 narrateur|Papa raconte une étoile.
 narrateur|L'étoile marche tout doucement.
+narrateur|Elle pose un pied, puis l'autre.
+enfant-m|Elle va où, papa ?
+papa|Vers le mur. Tout près.
 narrateur|Amir écoute.
 maman|C'est le dodo.
 maman|Le corps a besoin de dormir.
@@ -1365,7 +1376,6 @@
 papa|Le soir, on se couche.
 enfant-m|Pyjama, puis dodo.
 papa|Oui. Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Amir ferme les yeux.
 narrateur|Il respire doucement.
 narrateur|L'étoile jaune reste allumée.
@@ -1374,7 +1384,6 @@
 narrateur|C'est le dodo.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1404,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Simon va dormir. Que met-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir va dormir. Que met-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1559,7 +1568,6 @@
 narrateur|Que met-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1589,7 +1597,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Simon a mis le pyjama. Il s'est couché. Le &lt;emphasis level="moderate"&gt;soir&lt;/emphasis&gt;, c'est le dodo. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a mis le pyjama. Il s'est couché. Tu as mis le pyjama ? Oui. Le gris. Bravo, Amir. Le soir, c'est le dodo. L'étoile fait encore son rond.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1737,7 +1745,6 @@
 narrateur|L'étoile fait encore son rond.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1762,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tu es bien couché ? Oui, papa. Papa reste un moment. Maman baisse un peu l'étoile. Le rond devient tout petit. Amir respire. Le pyjama est chaud. Les pantoufles attendent encore.</t>
+          <t>Tu es bien couché ? Oui, papa. Papa reste un moment. Sa main est chaude sur la couverture. Je baisse un peu l'étoile. Le rond devient tout petit. Amir respire. Le pyjama est chaud. Les pantoufles attendent encore. Tu as encore soif ? Non, maman. D'accord. Bon dodo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Simon dort. Le &lt;emphasis level="moderate"&gt;pyjama&lt;/emphasis&gt; est chaud. La chambre est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Tu es bien couché ? Oui, papa. Papa reste un moment. Sa main est chaude sur la couverture. Je baisse un peu l'étoile. Le rond devient tout petit. Amir respire. Le pyjama est chaud. Les pantoufles attendent encore. Tu as encore soif ? Non, maman. D'accord. Bon dodo.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1905,14 +1912,17 @@
           <t>papa|Tu es bien couché ?
 enfant-m|Oui, papa.
 narrateur|Papa reste un moment.
-narrateur|Maman baisse un peu l'étoile.
+narrateur|Sa main est chaude sur la couverture.
+maman|Je baisse un peu l'étoile.
 narrateur|Le rond devient tout petit.
 narrateur|Amir respire.
 narrateur|Le pyjama est chaud.
-narrateur|Les pantoufles attendent encore.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|Les pantoufles attendent encore.
+maman|Tu as encore soif ?
+enfant-m|Non, maman.
+maman|D'accord. Bon dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1937,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai mis le pyjama. Bravo. Tu as fait du bon travail. L'étoile veille. L'histoire est finie.</t>
+          <t>J'ai mis le pyjama. Bravo. L'étoile veille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai mis le pyjama. Bravo. L'étoile veille.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2079,12 +2089,9 @@
         <is>
           <t>enfant-m|J'ai mis le pyjama.
 maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|L'étoile veille.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|L'étoile veille.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2103,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2148,6 +2155,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.SOM.001-05.xlsx
+++ b/stories/arbres/ATOM-SAN.SOM.001-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Simon, maman, papa</t>
+          <t>Amir, maman, papa</t>
         </is>
       </c>
     </row>
